--- a/rover_platform_mbse/export/ROVER-A1-ROVER_SAFETY-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_SAFETY-SWRS-V-001.xlsx
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_SAFETY-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_SAFETY-SWRS-V-001.xlsx
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_SAFETY-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_SAFETY-SWRS-V-001.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The rover_safety shall, in rover_safety_node, subscribe rover_battery/battery_status (sensor_msgs/BatteryState, KeepLast(1), reliable), hardware_interface/safety_command_echo (rover_msgs/SafetyCommandEcho, KeepLast(1), reliable, volatile), system_status (rover_msgs/SystemStatus, KeepLast(1), reliable) and hardware_interface/rover_driver_state (rover_msgs/RoverDriverState, depth 10), and act as a client of hardware_interface/sw_user_e_stop_set (std_srvs/Trigger).</t>
+          <t>The rover_safety shall, in rover_safety_node, subscribe battery/battery_status (sensor_msgs/BatteryState, KeepLast(1), reliable), hardware_interface/safety_command_echo (rover_msgs/SafetyCommandEcho, KeepLast(1), reliable, volatile), system_status (rover_msgs/SystemStatus, KeepLast(1), reliable) and hardware_interface/driver_state (rover_msgs/RoverDriverState, depth 10), and act as a client of hardware_interface/sw_user_e_stop_set (std_srvs/Trigger).</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>The rover_safety shall, in rover_safety_node, evaluate motor-driver temperature from hardware_interface/rover_driver_state and trip the software E-Stop above a driver temperature limit of [TBD] degC.</t>
+          <t>The rover_safety shall, in rover_safety_node, evaluate motor-driver temperature from hardware_interface/driver_state and trip the software E-Stop above a driver temperature limit of [TBD] degC.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>The rover_safety shall, in rover_led_safety_node, subscribe rover_battery/battery_status (depth 10), hardware_interface/safety_status (KeepLast(1), reliable, volatile) and joy (sensor_msgs/Joy, depth 10), tick the RoverLedSafety tree at timer_frequency (10.0 Hz) once e_stop_state and battery_status have been received, and request animations via led/set_animation (rover_msgs/SetLedAnimation) only when the selected animation changes.</t>
+          <t>The rover_safety shall, in rover_led_safety_node, subscribe battery/battery_status (depth 10), hardware_interface/safety_status (KeepLast(1), reliable, volatile) and joy (sensor_msgs/Joy, depth 10), tick the RoverLedSafety tree at timer_frequency (10.0 Hz) once e_stop_state and battery_status have been received, and request animations via led/set_animation (rover_msgs/SetLedAnimation) only when the selected animation changes.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
